--- a/results/andar_할인율모니터링_20260810.xlsx
+++ b/results/andar_할인율모니터링_20260810.xlsx
@@ -461,42 +461,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9023&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5845&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EMTBG-03</t>
+          <t>EJFMT-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>숄더 앤 크로스백</t>
+          <t>릴렉스 에어소프트 요가매트 (8mm)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7,154</t>
+          <t>9,923</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -713,42 +713,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5845&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9023&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EJFMT-01</t>
+          <t>EMTBG-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>릴렉스 에어소프트 요가매트 (8mm)</t>
+          <t>숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9,921</t>
+          <t>7,158</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -797,42 +797,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EPTBG-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>에어플라이 프리런 러닝 벨트</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2,169</t>
+          <t>2,170</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1007,42 +1007,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPTBG-01</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>에어플라이 프리런 러닝 벨트</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -1091,84 +1091,84 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>필라테스 토삭스</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>1,083</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>필라테스 토삭스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -1385,168 +1385,168 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EOTBG-13</t>
+          <t>EMTSC-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>멀티 포켓 숄더 앤 크로스백</t>
+          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>54,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>4,758</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EMTSC-03</t>
+          <t>EOTBG-13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
+          <t>멀티 포켓 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>54,000</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4,757</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EOTBG-23</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EOTBG-03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>데이 앤 트래블 숄더백</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1595,168 +1595,168 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EOTBG-03</t>
+          <t>EOTBG-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>데이 앤 트래블 숄더백</t>
+          <t>안다르 실버 리유저블백</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>EOTBG-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>폴더블 미니백 2.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>33,000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16636&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EPTFB-01</t>
+          <t>EOTCP-01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 헤드밴드</t>
+          <t>올라운드 버킷햇</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16636&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EOTBG-16</t>
+          <t>EPTFB-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>폴더블 미니백 2.0</t>
+          <t>퍼포먼스 심리스 헤드밴드</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>33,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10,268</t>
+          <t>10,269</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2015,121 +2015,121 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>[1&amp;1] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>1,931</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 무릎 보호대</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1,930</t>
+          <t>627</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>EOTET-01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>소프트 뱀부 롱 타월</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2183,37 +2183,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EOTET-01</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>소프트 뱀부 롱 타월</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>633</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2309,79 +2309,79 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EPTBG-02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>서밋 유틸리티 백팩</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3,900</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6,466</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EPTBG-02</t>
+          <t>EOTBG-15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>서밋 유틸리티 백팩</t>
+          <t>폴더블 짐백 2.0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2393,79 +2393,79 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EOTBG-15</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>폴더블 짐백 2.0</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6,466</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EPTBG-04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>드라이 페더 버킷백</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3,124</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2477,101 +2477,101 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3,124</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EPTBG-04</t>
+          <t>EPTCP-03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>드라이 페더 버킷백</t>
+          <t>썬가드 와이드 버킷햇</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2581,59 +2581,59 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1,341</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1,340</t>
+          <t>3,125</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2645,121 +2645,121 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8726&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EMTSC-03</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>논슬립 서포트 풀 토삭스 (HOLE)</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4,757</t>
+          <t>3,125</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8726&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EPTCP-03</t>
+          <t>EMTSC-03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>썬가드 와이드 버킷햇</t>
+          <t>논슬립 서포트 풀 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4,758</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>188</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2771,37 +2771,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>ENTBG-13</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>데일리 스퀘어백</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>401</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2813,37 +2813,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENTBG-13</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>데일리 스퀘어백</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2981,37 +2981,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>EOTSC-15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>논슬립 퍼포먼스 풀 토삭스</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3065,37 +3065,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EOTSC-15</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 풀 토삭스</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>797</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3191,111 +3191,111 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15145&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17446&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EOTBG-18</t>
+          <t>EPTSV-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>액티브 메쉬쿠션 슬링백</t>
+          <t>[1&amp;1] 3D 쿨링 핑거홀 팔토시</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>31,800</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17446&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15145&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EPTSV-01</t>
+          <t>EOTBG-18</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 핑거홀 팔토시</t>
+          <t>액티브 메쉬쿠션 슬링백</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>31,800</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3305,175 +3305,175 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>666</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EMTRB-01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>1,330</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>EMTRB-02</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1,052</t>
+          <t>1,330</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>EMTRB-03</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>6,900</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>6,500</t>
-        </is>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>1,330</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EMTRB-01</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1,330</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3485,84 +3485,84 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EMTRB-02</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1,330</t>
+          <t>1,053</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EMTRB-03</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1,330</t>
+          <t>656</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -3695,42 +3695,42 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EOTBG-17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>3 in 1 캐리온 더플백</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>109,000</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -3779,79 +3779,79 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EOTBG-19</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>위켄드 호보백</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>689</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EPTSC-01</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>쿨 메쉬 서포트 러닝 삭스</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2,993</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3905,163 +3905,163 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EOTBG-17</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3 in 1 캐리온 더플백</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2,993</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EPTET-03</t>
+          <t>EOTBG-19</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>안다르 3단 양우산</t>
+          <t>위켄드 호보백</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>EPTET-03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>안다르 3단 양우산</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>453</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4073,121 +4073,121 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ENTSC-10</t>
+          <t>ENTMT-01</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>더블 링글 라이트 크루 삭스</t>
+          <t>레스트 인 마블 요가매트 (4mm)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENTMT-01</t>
+          <t>EMTET-02</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>레스트 인 마블 요가매트 (4mm)</t>
+          <t>소프트 쿠셔닝 훌라후프</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>577</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2,069</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4199,121 +4199,121 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EMTSC-27</t>
+          <t>ENTSC-10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>올라운드 오버 니삭스</t>
+          <t>더블 링글 라이트 크루 삭스</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EMTSC-27</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>올라운드 오버 니삭스</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EMTET-02</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>소프트 쿠셔닝 훌라후프</t>
+          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4325,37 +4325,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EPTSV-02</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>2,069</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4409,163 +4409,163 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>326</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>196</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>37,600</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>531</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4577,79 +4577,79 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>ENTSC-20</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>시그니처 로고 크루 삭스</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EOTSC-13</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>테이핑 테크 러닝 삭스</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>37,600</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>587</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4661,84 +4661,84 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ENTSC-20</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>시그니처 로고 크루 삭스</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>EOTSC-13</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>테이핑 테크 러닝 삭스</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4787,84 +4787,84 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11362&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ENTBG-06</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>올데이 투웨이 슬링백</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>164</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11362&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>ENTBG-06</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>올데이 투웨이 슬링백</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4913,121 +4913,121 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ENTET-01</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>소프트 뱀부 스포츠 타월</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>ENTET-01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>소프트 뱀부 스포츠 타월</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5039,37 +5039,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5081,79 +5081,79 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ENTET-02</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 2kg</t>
+          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>581</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5165,126 +5165,126 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EMTSC-17</t>
+          <t>ENTET-02</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[3 SET] 맨즈 클래식 삭스</t>
+          <t>릴렉스 소프트 웨이트바 2kg</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20,700</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EMTSC-17</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>[3 SET] 맨즈 클래식 삭스</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>4,130</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5333,168 +5333,168 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4,130</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>하이 서포트 무릎 보호대</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>666</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 발목 보호대</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -5543,42 +5543,42 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>[1&amp;1] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5627,168 +5627,168 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>서포트 무릎 보호대</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1,930</t>
+          <t>635</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>13,900</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>12,900</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>10,900</t>
-        </is>
-      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>1,931</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5837,69 +5837,69 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EOTGL-02</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>히트 런 글러브</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EOTGL-02</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>히트 런 글러브</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5963,22 +5963,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EPTSC-01</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>쿨 메쉬 서포트 러닝 삭스</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5988,17 +5988,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>585</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6089,37 +6089,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>램스울 크루 삭스</t>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>587</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6131,42 +6131,42 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EOTMU-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 1kg</t>
+          <t>스트링 패딩 넥워머</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6215,42 +6215,42 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EOTMU-01</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>스트링 패딩 넥워머</t>
+          <t>하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>149</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -6299,17 +6299,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6383,17 +6383,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6403,133 +6403,133 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>385</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EOTMK-02</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>소프텐션 넥마스크</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EOTMK-02</t>
+          <t>ENTFB-04</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>소프텐션 넥마스크</t>
+          <t>더블 링글 손목밴드</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>4,500</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>422</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EOTCP-02</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>데님 로고 볼캡</t>
+          <t>램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6551,37 +6551,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EOTCP-02</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>하이 서포트 팔꿈치 보호대</t>
+          <t>데님 로고 볼캡</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6593,59 +6593,59 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ENTFB-04</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>더블 링글 손목밴드</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11208&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ENTSC-21</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>링글 오버 니삭스</t>
+          <t>서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6655,39 +6655,39 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>581</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11208&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>ENTSC-21</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>링글 오버 니삭스</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6697,143 +6697,143 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>서포트 팔꿈치 보호대</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>385</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>리브드 셔링 루즈 삭스</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7475,27 +7475,27 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>레그 숏 워머</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7505,39 +7505,39 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7547,12 +7547,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>352</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
